--- a/public/downloads/moving-company-quote-template.xlsx
+++ b/public/downloads/moving-company-quote-template.xlsx
@@ -531,7 +531,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F34"/>
+  <dimension ref="A1:G38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -540,6 +540,7 @@
     <col width="16" customWidth="1" min="4" max="4"/>
     <col width="14" customWidth="1" min="5" max="5"/>
     <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="10" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
@@ -687,6 +688,11 @@
           <t>Amount ($)</t>
         </is>
       </c>
+      <c r="G16" s="7" t="inlineStr">
+        <is>
+          <t>Taxable</t>
+        </is>
+      </c>
     </row>
     <row r="17" ht="18" customHeight="1">
       <c r="A17" s="9" t="n">
@@ -712,6 +718,9 @@
         <f>C17*E17</f>
         <v/>
       </c>
+      <c r="G17" s="9" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="18" ht="18" customHeight="1">
       <c r="A18" s="9" t="n">
@@ -737,6 +746,9 @@
         <f>C18*E18</f>
         <v/>
       </c>
+      <c r="G18" s="9" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="19" ht="18" customHeight="1">
       <c r="A19" s="9" t="n">
@@ -762,6 +774,9 @@
         <f>C19*E19</f>
         <v/>
       </c>
+      <c r="G19" s="9" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="20" ht="18" customHeight="1">
       <c r="A20" s="9" t="n">
@@ -787,6 +802,9 @@
         <f>C20*E20</f>
         <v/>
       </c>
+      <c r="G20" s="9" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="21" ht="18" customHeight="1">
       <c r="A21" s="9" t="n">
@@ -812,6 +830,9 @@
         <f>C21*E21</f>
         <v/>
       </c>
+      <c r="G21" s="9" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="22" ht="18" customHeight="1">
       <c r="A22" s="9" t="n">
@@ -837,6 +858,9 @@
         <f>C22*E22</f>
         <v/>
       </c>
+      <c r="G22" s="9" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="24">
       <c r="D24" s="3" t="inlineStr">
@@ -895,31 +919,57 @@
         </is>
       </c>
     </row>
-    <row r="30" ht="30" customHeight="1">
+    <row r="30">
       <c r="A30" s="3" t="inlineStr">
         <is>
+          <t>PAYMENT:</t>
+        </is>
+      </c>
+      <c r="B30" s="4" t="inlineStr">
+        <is>
+          <t>Make checks payable to: ______</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="B31" s="4" t="inlineStr">
+        <is>
+          <t>Card / Venmo / Zelle: ______</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="B32" s="4" t="inlineStr">
+        <is>
+          <t>Pay online: ______</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="30" customHeight="1">
+      <c r="A34" s="3" t="inlineStr">
+        <is>
           <t>NOTICE:</t>
         </is>
       </c>
-      <c r="B30" s="4" t="inlineStr">
+      <c r="B34" s="4" t="inlineStr">
         <is>
           <t>This is a quote, not an invoice. Pricing valid for 30 days; final charges may vary.</t>
         </is>
       </c>
     </row>
-    <row r="32">
-      <c r="A32" s="16" t="inlineStr">
+    <row r="36">
+      <c r="A36" s="16" t="inlineStr">
         <is>
           <t>Template for informational purposes only; does not constitute legal, tax, or accounting advice. Requirements vary by state — verify with your moving authority and CPA/attorney.</t>
         </is>
       </c>
     </row>
-    <row r="33"/>
-    <row r="34"/>
+    <row r="37"/>
+    <row r="38"/>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A32:F34"/>
+    <mergeCell ref="A36:F38"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/public/downloads/moving-company-quote-template.xlsx
+++ b/public/downloads/moving-company-quote-template.xlsx
@@ -9,7 +9,9 @@
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Invoice" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
-  <definedNames/>
+  <definedNames>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'Invoice'!$A$1:$F$38</definedName>
+  </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
@@ -529,7 +531,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:G38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
@@ -540,7 +542,7 @@
     <col width="16" customWidth="1" min="4" max="4"/>
     <col width="14" customWidth="1" min="5" max="5"/>
     <col width="14" customWidth="1" min="6" max="6"/>
-    <col width="10" customWidth="1" min="7" max="7"/>
+    <col hidden="1" width="10" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
@@ -972,5 +974,6 @@
     <mergeCell ref="A36:F38"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="portrait" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
 </file>